--- a/ExcelRAddIn/Tests/PCA Scree Plot.xlsx
+++ b/ExcelRAddIn/Tests/PCA Scree Plot.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Projects\C#\Office\Office365 AddIns\ExcelRAddIn\Tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBECF84-39DF-420D-B3F0-2AA15434A942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F30968B-6434-4B3E-A024-CC3A9076B3E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{F2739E45-92FD-4566-89DF-9450CE0F6384}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -198,9 +198,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -238,7 +238,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -344,7 +344,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -486,7 +486,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3650,11 +3650,11 @@
         <v>1</v>
       </c>
       <c r="G11">
-        <v>2.9184978165319944</v>
+        <v>2.918497816531997</v>
       </c>
       <c r="H11">
         <f>G11/SUM($G$11:$G$14)</f>
-        <v>0.72962445413299903</v>
+        <v>0.72962445413299892</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
@@ -3662,11 +3662,11 @@
         <v>2</v>
       </c>
       <c r="G12">
-        <v>0.91403047146806948</v>
+        <v>0.91403047146807026</v>
       </c>
       <c r="H12">
         <f t="shared" ref="H12:H14" si="0">G12/SUM($G$11:$G$14)</f>
-        <v>0.22850761786701751</v>
+        <v>0.22850761786701745</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
@@ -3674,11 +3674,11 @@
         <v>3</v>
       </c>
       <c r="G13">
-        <v>0.14675687557131503</v>
+        <v>0.146756875571315</v>
       </c>
       <c r="H13">
         <f t="shared" si="0"/>
-        <v>3.6689218892828779E-2</v>
+        <v>3.6689218892828737E-2</v>
       </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.3">
@@ -3686,11 +3686,11 @@
         <v>4</v>
       </c>
       <c r="G14">
-        <v>2.0714836428619265E-2</v>
+        <v>2.0714836428619241E-2</v>
       </c>
       <c r="H14">
         <f t="shared" si="0"/>
-        <v>5.178709107154819E-3</v>
+        <v>5.1787091071548077E-3</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.3">
